--- a/artfynd/A 54612-2021 artfynd.xlsx
+++ b/artfynd/A 54612-2021 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 54612-2021 artfynd.xlsx
+++ b/artfynd/A 54612-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY8"/>
+  <dimension ref="A1:AY12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1536,6 +1536,450 @@
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>120288193</v>
+      </c>
+      <c r="B9" t="n">
+        <v>100188</v>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>1853</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Mosippa</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Pulsatilla vernalis</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(L.) Mill.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Vassbo, Dlr</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>373367</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6869827</v>
+      </c>
+      <c r="S9" t="n">
+        <v>5</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Idre</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2021-09-23</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2021-09-23</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering.</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>120288150</v>
+      </c>
+      <c r="B10" t="n">
+        <v>100188</v>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>1853</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Mosippa</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Pulsatilla vernalis</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(L.) Mill.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Höstsätern, Dlr</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>373598</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6869623</v>
+      </c>
+      <c r="S10" t="n">
+        <v>6</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Idre</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2021-09-27</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2021-09-27</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering.</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>120288194</v>
+      </c>
+      <c r="B11" t="n">
+        <v>91834</v>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>4362</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Blå taggsvamp</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Hydnellum caeruleum</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(Hornem.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Vassbo, Dlr</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>373422</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6869900</v>
+      </c>
+      <c r="S11" t="n">
+        <v>6</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Idre</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2021-09-23</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2021-09-23</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering.</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>120288151</v>
+      </c>
+      <c r="B12" t="n">
+        <v>100188</v>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>1853</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Mosippa</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Pulsatilla vernalis</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(L.) Mill.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Vassbo, Dlr</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>373501</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6869652</v>
+      </c>
+      <c r="S12" t="n">
+        <v>6</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Idre</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2021-09-27</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2021-09-27</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering.</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 54612-2021 artfynd.xlsx
+++ b/artfynd/A 54612-2021 artfynd.xlsx
@@ -1538,10 +1538,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>120288193</v>
+        <v>120288150</v>
       </c>
       <c r="B9" t="n">
-        <v>100188</v>
+        <v>100211</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1578,17 +1578,17 @@
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Vassbo, Dlr</t>
+          <t>Höstsätern, Dlr</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>373367</v>
+        <v>373598</v>
       </c>
       <c r="R9" t="n">
-        <v>6869827</v>
+        <v>6869623</v>
       </c>
       <c r="S9" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1612,12 +1612,12 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2021-09-23</t>
+          <t>2021-09-27</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2021-09-23</t>
+          <t>2021-09-27</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
@@ -1649,10 +1649,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>120288150</v>
+        <v>120288194</v>
       </c>
       <c r="B10" t="n">
-        <v>100188</v>
+        <v>91852</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1661,25 +1661,25 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1853</v>
+        <v>4362</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Mosippa</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Pulsatilla vernalis</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) Mill.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1689,14 +1689,14 @@
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Höstsätern, Dlr</t>
+          <t>Vassbo, Dlr</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>373598</v>
+        <v>373422</v>
       </c>
       <c r="R10" t="n">
-        <v>6869623</v>
+        <v>6869900</v>
       </c>
       <c r="S10" t="n">
         <v>6</v>
@@ -1723,12 +1723,12 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2021-09-27</t>
+          <t>2021-09-23</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2021-09-27</t>
+          <t>2021-09-23</t>
         </is>
       </c>
       <c r="AC10" t="inlineStr">
@@ -1760,10 +1760,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>120288194</v>
+        <v>120288151</v>
       </c>
       <c r="B11" t="n">
-        <v>91834</v>
+        <v>100211</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1772,25 +1772,25 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>4362</v>
+        <v>1853</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Mosippa</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Pulsatilla vernalis</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(L.) Mill.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1804,10 +1804,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>373422</v>
+        <v>373501</v>
       </c>
       <c r="R11" t="n">
-        <v>6869900</v>
+        <v>6869652</v>
       </c>
       <c r="S11" t="n">
         <v>6</v>
@@ -1834,12 +1834,12 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2021-09-23</t>
+          <t>2021-09-27</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2021-09-23</t>
+          <t>2021-09-27</t>
         </is>
       </c>
       <c r="AC11" t="inlineStr">
@@ -1871,10 +1871,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>120288151</v>
+        <v>120288193</v>
       </c>
       <c r="B12" t="n">
-        <v>100188</v>
+        <v>100211</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1915,13 +1915,13 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>373501</v>
+        <v>373367</v>
       </c>
       <c r="R12" t="n">
-        <v>6869652</v>
+        <v>6869827</v>
       </c>
       <c r="S12" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1945,12 +1945,12 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2021-09-27</t>
+          <t>2021-09-23</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2021-09-27</t>
+          <t>2021-09-23</t>
         </is>
       </c>
       <c r="AC12" t="inlineStr">

--- a/artfynd/A 54612-2021 artfynd.xlsx
+++ b/artfynd/A 54612-2021 artfynd.xlsx
@@ -1538,10 +1538,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>120288150</v>
+        <v>120288194</v>
       </c>
       <c r="B9" t="n">
-        <v>100211</v>
+        <v>91852</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1550,25 +1550,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1853</v>
+        <v>4362</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Mosippa</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Pulsatilla vernalis</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) Mill.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1578,14 +1578,14 @@
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Höstsätern, Dlr</t>
+          <t>Vassbo, Dlr</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>373598</v>
+        <v>373422</v>
       </c>
       <c r="R9" t="n">
-        <v>6869623</v>
+        <v>6869900</v>
       </c>
       <c r="S9" t="n">
         <v>6</v>
@@ -1612,12 +1612,12 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2021-09-27</t>
+          <t>2021-09-23</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2021-09-27</t>
+          <t>2021-09-23</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
@@ -1649,10 +1649,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>120288194</v>
+        <v>120288151</v>
       </c>
       <c r="B10" t="n">
-        <v>91852</v>
+        <v>100211</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1661,25 +1661,25 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>4362</v>
+        <v>1853</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Mosippa</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Pulsatilla vernalis</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(L.) Mill.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1693,10 +1693,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>373422</v>
+        <v>373501</v>
       </c>
       <c r="R10" t="n">
-        <v>6869900</v>
+        <v>6869652</v>
       </c>
       <c r="S10" t="n">
         <v>6</v>
@@ -1723,12 +1723,12 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2021-09-23</t>
+          <t>2021-09-27</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2021-09-23</t>
+          <t>2021-09-27</t>
         </is>
       </c>
       <c r="AC10" t="inlineStr">
@@ -1760,7 +1760,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>120288151</v>
+        <v>120288193</v>
       </c>
       <c r="B11" t="n">
         <v>100211</v>
@@ -1804,13 +1804,13 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>373501</v>
+        <v>373367</v>
       </c>
       <c r="R11" t="n">
-        <v>6869652</v>
+        <v>6869827</v>
       </c>
       <c r="S11" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1834,12 +1834,12 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2021-09-27</t>
+          <t>2021-09-23</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2021-09-27</t>
+          <t>2021-09-23</t>
         </is>
       </c>
       <c r="AC11" t="inlineStr">
@@ -1871,7 +1871,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>120288193</v>
+        <v>120288150</v>
       </c>
       <c r="B12" t="n">
         <v>100211</v>
@@ -1911,17 +1911,17 @@
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Vassbo, Dlr</t>
+          <t>Höstsätern, Dlr</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>373367</v>
+        <v>373598</v>
       </c>
       <c r="R12" t="n">
-        <v>6869827</v>
+        <v>6869623</v>
       </c>
       <c r="S12" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1945,12 +1945,12 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2021-09-23</t>
+          <t>2021-09-27</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2021-09-23</t>
+          <t>2021-09-27</t>
         </is>
       </c>
       <c r="AC12" t="inlineStr">

--- a/artfynd/A 54612-2021 artfynd.xlsx
+++ b/artfynd/A 54612-2021 artfynd.xlsx
@@ -1538,10 +1538,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>120288194</v>
+        <v>120288150</v>
       </c>
       <c r="B9" t="n">
-        <v>91852</v>
+        <v>100211</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1550,25 +1550,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>4362</v>
+        <v>1853</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Mosippa</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Pulsatilla vernalis</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(L.) Mill.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1578,14 +1578,14 @@
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Vassbo, Dlr</t>
+          <t>Höstsätern, Dlr</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>373422</v>
+        <v>373598</v>
       </c>
       <c r="R9" t="n">
-        <v>6869900</v>
+        <v>6869623</v>
       </c>
       <c r="S9" t="n">
         <v>6</v>
@@ -1612,12 +1612,12 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2021-09-23</t>
+          <t>2021-09-27</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2021-09-23</t>
+          <t>2021-09-27</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
@@ -1649,10 +1649,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>120288151</v>
+        <v>120288194</v>
       </c>
       <c r="B10" t="n">
-        <v>100211</v>
+        <v>91852</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1661,25 +1661,25 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1853</v>
+        <v>4362</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Mosippa</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Pulsatilla vernalis</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) Mill.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1693,10 +1693,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>373501</v>
+        <v>373422</v>
       </c>
       <c r="R10" t="n">
-        <v>6869652</v>
+        <v>6869900</v>
       </c>
       <c r="S10" t="n">
         <v>6</v>
@@ -1723,12 +1723,12 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2021-09-27</t>
+          <t>2021-09-23</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2021-09-27</t>
+          <t>2021-09-23</t>
         </is>
       </c>
       <c r="AC10" t="inlineStr">
@@ -1760,7 +1760,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>120288193</v>
+        <v>120288151</v>
       </c>
       <c r="B11" t="n">
         <v>100211</v>
@@ -1804,13 +1804,13 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>373367</v>
+        <v>373501</v>
       </c>
       <c r="R11" t="n">
-        <v>6869827</v>
+        <v>6869652</v>
       </c>
       <c r="S11" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1834,12 +1834,12 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2021-09-23</t>
+          <t>2021-09-27</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2021-09-23</t>
+          <t>2021-09-27</t>
         </is>
       </c>
       <c r="AC11" t="inlineStr">
@@ -1871,7 +1871,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>120288150</v>
+        <v>120288193</v>
       </c>
       <c r="B12" t="n">
         <v>100211</v>
@@ -1911,17 +1911,17 @@
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Höstsätern, Dlr</t>
+          <t>Vassbo, Dlr</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>373598</v>
+        <v>373367</v>
       </c>
       <c r="R12" t="n">
-        <v>6869623</v>
+        <v>6869827</v>
       </c>
       <c r="S12" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1945,12 +1945,12 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2021-09-27</t>
+          <t>2021-09-23</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2021-09-27</t>
+          <t>2021-09-23</t>
         </is>
       </c>
       <c r="AC12" t="inlineStr">

--- a/artfynd/A 54612-2021 artfynd.xlsx
+++ b/artfynd/A 54612-2021 artfynd.xlsx
@@ -1538,10 +1538,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>120288194</v>
+        <v>120288151</v>
       </c>
       <c r="B9" t="n">
-        <v>91852</v>
+        <v>100211</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1550,25 +1550,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>4362</v>
+        <v>1853</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Mosippa</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Pulsatilla vernalis</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(L.) Mill.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1582,10 +1582,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>373422</v>
+        <v>373501</v>
       </c>
       <c r="R9" t="n">
-        <v>6869900</v>
+        <v>6869652</v>
       </c>
       <c r="S9" t="n">
         <v>6</v>
@@ -1612,12 +1612,12 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2021-09-23</t>
+          <t>2021-09-27</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2021-09-23</t>
+          <t>2021-09-27</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
@@ -1649,7 +1649,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>120288151</v>
+        <v>120288193</v>
       </c>
       <c r="B10" t="n">
         <v>100211</v>
@@ -1693,13 +1693,13 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>373501</v>
+        <v>373367</v>
       </c>
       <c r="R10" t="n">
-        <v>6869652</v>
+        <v>6869827</v>
       </c>
       <c r="S10" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1723,12 +1723,12 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2021-09-27</t>
+          <t>2021-09-23</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2021-09-27</t>
+          <t>2021-09-23</t>
         </is>
       </c>
       <c r="AC10" t="inlineStr">
@@ -1760,10 +1760,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>120288193</v>
+        <v>120288194</v>
       </c>
       <c r="B11" t="n">
-        <v>100211</v>
+        <v>91852</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1772,25 +1772,25 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1853</v>
+        <v>4362</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Mosippa</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Pulsatilla vernalis</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) Mill.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1804,13 +1804,13 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>373367</v>
+        <v>373422</v>
       </c>
       <c r="R11" t="n">
-        <v>6869827</v>
+        <v>6869900</v>
       </c>
       <c r="S11" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>

--- a/artfynd/A 54612-2021 artfynd.xlsx
+++ b/artfynd/A 54612-2021 artfynd.xlsx
@@ -1538,7 +1538,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>120288151</v>
+        <v>120288150</v>
       </c>
       <c r="B9" t="n">
         <v>100211</v>
@@ -1578,14 +1578,14 @@
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Vassbo, Dlr</t>
+          <t>Höstsätern, Dlr</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>373501</v>
+        <v>373598</v>
       </c>
       <c r="R9" t="n">
-        <v>6869652</v>
+        <v>6869623</v>
       </c>
       <c r="S9" t="n">
         <v>6</v>
@@ -1649,7 +1649,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>120288193</v>
+        <v>120288151</v>
       </c>
       <c r="B10" t="n">
         <v>100211</v>
@@ -1693,13 +1693,13 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>373367</v>
+        <v>373501</v>
       </c>
       <c r="R10" t="n">
-        <v>6869827</v>
+        <v>6869652</v>
       </c>
       <c r="S10" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1723,12 +1723,12 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2021-09-23</t>
+          <t>2021-09-27</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2021-09-23</t>
+          <t>2021-09-27</t>
         </is>
       </c>
       <c r="AC10" t="inlineStr">
@@ -1760,10 +1760,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>120288194</v>
+        <v>120288193</v>
       </c>
       <c r="B11" t="n">
-        <v>91852</v>
+        <v>100211</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1772,25 +1772,25 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>4362</v>
+        <v>1853</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Mosippa</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Pulsatilla vernalis</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(L.) Mill.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1804,13 +1804,13 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>373422</v>
+        <v>373367</v>
       </c>
       <c r="R11" t="n">
-        <v>6869900</v>
+        <v>6869827</v>
       </c>
       <c r="S11" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1871,10 +1871,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>120288150</v>
+        <v>120288194</v>
       </c>
       <c r="B12" t="n">
-        <v>100211</v>
+        <v>91852</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1883,25 +1883,25 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1853</v>
+        <v>4362</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Mosippa</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Pulsatilla vernalis</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) Mill.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -1911,14 +1911,14 @@
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Höstsätern, Dlr</t>
+          <t>Vassbo, Dlr</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>373598</v>
+        <v>373422</v>
       </c>
       <c r="R12" t="n">
-        <v>6869623</v>
+        <v>6869900</v>
       </c>
       <c r="S12" t="n">
         <v>6</v>
@@ -1945,12 +1945,12 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2021-09-27</t>
+          <t>2021-09-23</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2021-09-27</t>
+          <t>2021-09-23</t>
         </is>
       </c>
       <c r="AC12" t="inlineStr">

--- a/artfynd/A 54612-2021 artfynd.xlsx
+++ b/artfynd/A 54612-2021 artfynd.xlsx
@@ -1538,7 +1538,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>120288150</v>
+        <v>120288193</v>
       </c>
       <c r="B9" t="n">
         <v>100211</v>
@@ -1578,17 +1578,17 @@
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Höstsätern, Dlr</t>
+          <t>Vassbo, Dlr</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>373598</v>
+        <v>373367</v>
       </c>
       <c r="R9" t="n">
-        <v>6869623</v>
+        <v>6869827</v>
       </c>
       <c r="S9" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1612,12 +1612,12 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2021-09-27</t>
+          <t>2021-09-23</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2021-09-27</t>
+          <t>2021-09-23</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
@@ -1649,10 +1649,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>120288151</v>
+        <v>120288194</v>
       </c>
       <c r="B10" t="n">
-        <v>100211</v>
+        <v>91852</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1661,25 +1661,25 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1853</v>
+        <v>4362</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Mosippa</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Pulsatilla vernalis</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) Mill.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1693,10 +1693,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>373501</v>
+        <v>373422</v>
       </c>
       <c r="R10" t="n">
-        <v>6869652</v>
+        <v>6869900</v>
       </c>
       <c r="S10" t="n">
         <v>6</v>
@@ -1723,12 +1723,12 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2021-09-27</t>
+          <t>2021-09-23</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2021-09-27</t>
+          <t>2021-09-23</t>
         </is>
       </c>
       <c r="AC10" t="inlineStr">
@@ -1760,7 +1760,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>120288193</v>
+        <v>120288151</v>
       </c>
       <c r="B11" t="n">
         <v>100211</v>
@@ -1804,13 +1804,13 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>373367</v>
+        <v>373501</v>
       </c>
       <c r="R11" t="n">
-        <v>6869827</v>
+        <v>6869652</v>
       </c>
       <c r="S11" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1834,12 +1834,12 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2021-09-23</t>
+          <t>2021-09-27</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2021-09-23</t>
+          <t>2021-09-27</t>
         </is>
       </c>
       <c r="AC11" t="inlineStr">
@@ -1871,10 +1871,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>120288194</v>
+        <v>120288150</v>
       </c>
       <c r="B12" t="n">
-        <v>91852</v>
+        <v>100211</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1883,25 +1883,25 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>4362</v>
+        <v>1853</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Mosippa</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Pulsatilla vernalis</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(L.) Mill.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -1911,14 +1911,14 @@
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Vassbo, Dlr</t>
+          <t>Höstsätern, Dlr</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>373422</v>
+        <v>373598</v>
       </c>
       <c r="R12" t="n">
-        <v>6869900</v>
+        <v>6869623</v>
       </c>
       <c r="S12" t="n">
         <v>6</v>
@@ -1945,12 +1945,12 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2021-09-23</t>
+          <t>2021-09-27</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2021-09-23</t>
+          <t>2021-09-27</t>
         </is>
       </c>
       <c r="AC12" t="inlineStr">

--- a/artfynd/A 54612-2021 artfynd.xlsx
+++ b/artfynd/A 54612-2021 artfynd.xlsx
@@ -1985,7 +1985,7 @@
         <v>96483507</v>
       </c>
       <c r="B13" t="n">
-        <v>57589</v>
+        <v>57592</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>

--- a/artfynd/A 54612-2021 artfynd.xlsx
+++ b/artfynd/A 54612-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY13"/>
+  <dimension ref="A1:AY12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1417,10 +1417,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>97909309</v>
+        <v>120288151</v>
       </c>
       <c r="B8" t="n">
-        <v>98536</v>
+        <v>100282</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1461,13 +1461,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>373501.1598564582</v>
+        <v>373501</v>
       </c>
       <c r="R8" t="n">
-        <v>6869652.500233497</v>
+        <v>6869652</v>
       </c>
       <c r="S8" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1491,22 +1491,12 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2021-10-01</t>
-        </is>
-      </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2021-09-27</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2021-10-01</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2021-09-27</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
@@ -1871,10 +1861,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>120288151</v>
+        <v>96483507</v>
       </c>
       <c r="B12" t="n">
-        <v>100282</v>
+        <v>57592</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1883,45 +1873,57 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1853</v>
+        <v>103031</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Mosippa</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Pulsatilla vernalis</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) Mill.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>i par</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr"/>
+      <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Vassbo, Dlr</t>
+          <t>NO Messmörloken, Dlr</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>373501</v>
+        <v>373216</v>
       </c>
       <c r="R12" t="n">
-        <v>6869652</v>
+        <v>6869575</v>
       </c>
       <c r="S12" t="n">
-        <v>6</v>
+        <v>25</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1945,17 +1947,22 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2021-09-27</t>
+          <t>2021-10-05</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>12:30</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2021-09-27</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Påträffad under Sveaskogs naturvärdesinventering.</t>
+          <t>2021-10-05</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>12:30</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1970,143 +1977,15 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Mimmi Persson</t>
+          <t>John-Olof Halvarsson</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Mimmi Persson</t>
+          <t>John-Olof Halvarsson</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
-    </row>
-    <row r="13">
-      <c r="A13" t="n">
-        <v>96483507</v>
-      </c>
-      <c r="B13" t="n">
-        <v>57592</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E13" t="n">
-        <v>103031</v>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>Lavskrika</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>Perisoreus infaustus</t>
-        </is>
-      </c>
-      <c r="H13" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K13" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L13" t="inlineStr">
-        <is>
-          <t>i par</t>
-        </is>
-      </c>
-      <c r="M13" t="inlineStr"/>
-      <c r="N13" t="inlineStr"/>
-      <c r="P13" t="inlineStr">
-        <is>
-          <t>NO Messmörloken, Dlr</t>
-        </is>
-      </c>
-      <c r="Q13" t="n">
-        <v>373216</v>
-      </c>
-      <c r="R13" t="n">
-        <v>6869575</v>
-      </c>
-      <c r="S13" t="n">
-        <v>25</v>
-      </c>
-      <c r="T13" t="inlineStr">
-        <is>
-          <t>Dalarna</t>
-        </is>
-      </c>
-      <c r="U13" t="inlineStr">
-        <is>
-          <t>Älvdalen</t>
-        </is>
-      </c>
-      <c r="V13" t="inlineStr">
-        <is>
-          <t>Dalarna</t>
-        </is>
-      </c>
-      <c r="W13" t="inlineStr">
-        <is>
-          <t>Idre</t>
-        </is>
-      </c>
-      <c r="Y13" t="inlineStr">
-        <is>
-          <t>2021-10-05</t>
-        </is>
-      </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>12:30</t>
-        </is>
-      </c>
-      <c r="AA13" t="inlineStr">
-        <is>
-          <t>2021-10-05</t>
-        </is>
-      </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>12:30</t>
-        </is>
-      </c>
-      <c r="AD13" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE13" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG13" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT13" t="inlineStr"/>
-      <c r="AW13" t="inlineStr">
-        <is>
-          <t>John-Olof Halvarsson</t>
-        </is>
-      </c>
-      <c r="AX13" t="inlineStr">
-        <is>
-          <t>John-Olof Halvarsson</t>
-        </is>
-      </c>
-      <c r="AY13" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
